--- a/DataTables/Datas/Character/#CardInfo.xlsx
+++ b/DataTables/Datas/Character/#CardInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Ashlight\DataTables\Datas\Character\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06626165-AB16-4F53-9E1F-965F4C146F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{620DE29E-DDED-4155-B8CA-93FD1C7C7EB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5760" yWindow="10530" windowWidth="21600" windowHeight="11333" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -172,9 +172,6 @@
     <t>守护</t>
   </si>
   <si>
-    <t>使友方角色获得 {D} 点高额护甲。</t>
-  </si>
-  <si>
     <t>InterceptEffect,D,20</t>
   </si>
   <si>
@@ -525,6 +522,10 @@
   </si>
   <si>
     <t>zxs n</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使友方角色获得 {D} 点护甲。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1010,7 +1011,7 @@
         <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E6" t="s">
         <v>37</v>
@@ -1115,10 +1116,10 @@
         <v>49</v>
       </c>
       <c r="D9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" t="s">
         <v>50</v>
-      </c>
-      <c r="E9" t="s">
-        <v>51</v>
       </c>
       <c r="F9" t="s">
         <v>29</v>
@@ -1127,7 +1128,7 @@
         <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I9" t="s">
         <v>32</v>
@@ -1144,16 +1145,16 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
         <v>53</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>54</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>55</v>
-      </c>
-      <c r="E10" t="s">
-        <v>56</v>
       </c>
       <c r="F10" t="s">
         <v>42</v>
@@ -1162,7 +1163,7 @@
         <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I10" t="s">
         <v>32</v>
@@ -1179,16 +1180,16 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" t="s">
         <v>58</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>59</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>60</v>
-      </c>
-      <c r="E11" t="s">
-        <v>61</v>
       </c>
       <c r="F11" t="s">
         <v>42</v>
@@ -1197,7 +1198,7 @@
         <v>30</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I11" t="s">
         <v>32</v>
@@ -1214,16 +1215,16 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
         <v>62</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>63</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>64</v>
-      </c>
-      <c r="E12" t="s">
-        <v>65</v>
       </c>
       <c r="F12" t="s">
         <v>42</v>
@@ -1249,16 +1250,16 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" t="s">
         <v>66</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>67</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>68</v>
-      </c>
-      <c r="E13" t="s">
-        <v>69</v>
       </c>
       <c r="F13" t="s">
         <v>42</v>
@@ -1284,13 +1285,13 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" t="s">
         <v>70</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>71</v>
-      </c>
-      <c r="D14" t="s">
-        <v>72</v>
       </c>
       <c r="E14" t="s">
         <v>28</v>
@@ -1299,7 +1300,7 @@
         <v>42</v>
       </c>
       <c r="G14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H14" t="s">
         <v>31</v>
@@ -1319,22 +1320,22 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" t="s">
         <v>74</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>75</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>76</v>
-      </c>
-      <c r="E15" t="s">
-        <v>77</v>
       </c>
       <c r="F15" t="s">
         <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H15" t="s">
         <v>31</v>
@@ -1354,22 +1355,22 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" t="s">
         <v>78</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>79</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>80</v>
-      </c>
-      <c r="E16" t="s">
-        <v>81</v>
       </c>
       <c r="F16" t="s">
         <v>29</v>
       </c>
       <c r="G16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H16" t="s">
         <v>43</v>
@@ -1389,25 +1390,25 @@
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
         <v>82</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>83</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>84</v>
-      </c>
-      <c r="E17" t="s">
-        <v>85</v>
       </c>
       <c r="F17" t="s">
         <v>29</v>
       </c>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I17" t="s">
         <v>32</v>
@@ -1424,22 +1425,22 @@
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" t="s">
         <v>86</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" t="s">
         <v>87</v>
-      </c>
-      <c r="D18" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" t="s">
-        <v>88</v>
       </c>
       <c r="F18" t="s">
         <v>42</v>
       </c>
       <c r="G18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H18" t="s">
         <v>31</v>
@@ -1459,22 +1460,22 @@
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
         <v>89</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>90</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>91</v>
-      </c>
-      <c r="E19" t="s">
-        <v>92</v>
       </c>
       <c r="F19" t="s">
         <v>42</v>
       </c>
       <c r="G19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H19" t="s">
         <v>43</v>
@@ -1494,22 +1495,22 @@
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" t="s">
         <v>93</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>94</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>95</v>
-      </c>
-      <c r="E20" t="s">
-        <v>96</v>
       </c>
       <c r="F20" t="s">
         <v>42</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H20" t="s">
         <v>31</v>
@@ -1529,22 +1530,22 @@
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" t="s">
         <v>97</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>98</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>99</v>
-      </c>
-      <c r="E21" t="s">
-        <v>100</v>
       </c>
       <c r="F21" t="s">
         <v>29</v>
       </c>
       <c r="G21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H21" t="s">
         <v>31</v>
@@ -1564,22 +1565,22 @@
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s">
         <v>101</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>102</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>103</v>
-      </c>
-      <c r="E22" t="s">
-        <v>104</v>
       </c>
       <c r="F22" t="s">
         <v>42</v>
       </c>
       <c r="G22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H22" t="s">
         <v>43</v>
@@ -1591,7 +1592,7 @@
         <v>33</v>
       </c>
       <c r="L22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M22">
         <v>3</v>
@@ -1599,22 +1600,22 @@
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
+        <v>105</v>
+      </c>
+      <c r="C23" t="s">
         <v>106</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>107</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>108</v>
-      </c>
-      <c r="E23" t="s">
-        <v>109</v>
       </c>
       <c r="F23" t="s">
         <v>42</v>
       </c>
       <c r="G23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" t="s">
         <v>43</v>
@@ -1626,7 +1627,7 @@
         <v>33</v>
       </c>
       <c r="L23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M23">
         <v>5</v>
@@ -1634,22 +1635,22 @@
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" t="s">
         <v>111</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>112</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>113</v>
-      </c>
-      <c r="E24" t="s">
-        <v>114</v>
       </c>
       <c r="F24" t="s">
         <v>29</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24" t="s">
         <v>31</v>
@@ -1669,22 +1670,22 @@
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" t="s">
         <v>115</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>116</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>117</v>
-      </c>
-      <c r="E25" t="s">
-        <v>118</v>
       </c>
       <c r="F25" t="s">
         <v>42</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H25" t="s">
         <v>31</v>
@@ -1696,7 +1697,7 @@
         <v>33</v>
       </c>
       <c r="L25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M25">
         <v>1</v>
@@ -1704,22 +1705,22 @@
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26" t="s">
         <v>119</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" t="s">
         <v>120</v>
-      </c>
-      <c r="D26" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" t="s">
-        <v>121</v>
       </c>
       <c r="F26" t="s">
         <v>29</v>
       </c>
       <c r="G26" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H26" t="s">
         <v>31</v>
@@ -1739,22 +1740,22 @@
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" t="s">
         <v>123</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>124</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>125</v>
-      </c>
-      <c r="E27" t="s">
-        <v>126</v>
       </c>
       <c r="F27" t="s">
         <v>42</v>
       </c>
       <c r="G27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H27" t="s">
         <v>31</v>
@@ -1774,22 +1775,22 @@
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" t="s">
         <v>127</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>128</v>
       </c>
-      <c r="D28" t="s">
+      <c r="E28" t="s">
         <v>129</v>
-      </c>
-      <c r="E28" t="s">
-        <v>130</v>
       </c>
       <c r="F28" t="s">
         <v>42</v>
       </c>
       <c r="G28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H28" t="s">
         <v>31</v>
@@ -1809,22 +1810,22 @@
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" t="s">
         <v>131</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>132</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>133</v>
-      </c>
-      <c r="E29" t="s">
-        <v>134</v>
       </c>
       <c r="F29" t="s">
         <v>42</v>
       </c>
       <c r="G29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H29" t="s">
         <v>43</v>
@@ -1844,22 +1845,22 @@
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
+        <v>134</v>
+      </c>
+      <c r="C30" t="s">
         <v>135</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>136</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>137</v>
-      </c>
-      <c r="E30" t="s">
-        <v>138</v>
       </c>
       <c r="F30" t="s">
         <v>42</v>
       </c>
       <c r="G30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H30" t="s">
         <v>31</v>
@@ -1879,22 +1880,22 @@
     </row>
     <row r="31" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" t="s">
         <v>139</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>140</v>
       </c>
-      <c r="D31" t="s">
-        <v>141</v>
-      </c>
       <c r="E31" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F31" t="s">
         <v>29</v>
       </c>
       <c r="G31" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H31" t="s">
         <v>31</v>
@@ -1914,22 +1915,22 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C32" t="s">
         <v>142</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
         <v>143</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>144</v>
-      </c>
-      <c r="E32" t="s">
-        <v>145</v>
       </c>
       <c r="F32" t="s">
         <v>42</v>
       </c>
       <c r="G32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H32" t="s">
         <v>31</v>
@@ -1949,22 +1950,22 @@
     </row>
     <row r="33" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C33" t="s">
         <v>146</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>147</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>148</v>
-      </c>
-      <c r="E33" t="s">
-        <v>149</v>
       </c>
       <c r="F33" t="s">
         <v>42</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H33" t="s">
         <v>31</v>
@@ -1984,22 +1985,22 @@
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
+        <v>149</v>
+      </c>
+      <c r="C34" t="s">
         <v>150</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
         <v>151</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>152</v>
-      </c>
-      <c r="E34" t="s">
-        <v>153</v>
       </c>
       <c r="F34" t="s">
         <v>42</v>
       </c>
       <c r="G34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H34" t="s">
         <v>31</v>
@@ -2019,22 +2020,22 @@
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" t="s">
         <v>154</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
         <v>155</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>156</v>
-      </c>
-      <c r="E35" t="s">
-        <v>157</v>
       </c>
       <c r="F35" t="s">
         <v>29</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H35" t="s">
         <v>31</v>
@@ -2052,30 +2053,30 @@
         <v>0</v>
       </c>
       <c r="S35" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
+        <v>157</v>
+      </c>
+      <c r="C36" t="s">
         <v>158</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
         <v>159</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>160</v>
-      </c>
-      <c r="E36" t="s">
-        <v>161</v>
       </c>
       <c r="F36" t="s">
         <v>29</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H36" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I36" t="s">
         <v>32</v>
@@ -2092,22 +2093,22 @@
     </row>
     <row r="37" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
+        <v>161</v>
+      </c>
+      <c r="C37" t="s">
         <v>162</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
         <v>163</v>
       </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>164</v>
-      </c>
-      <c r="E37" t="s">
-        <v>165</v>
       </c>
       <c r="F37" t="s">
         <v>42</v>
       </c>
       <c r="G37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H37" t="s">
         <v>31</v>

--- a/DataTables/Datas/Character/#CardInfo.xlsx
+++ b/DataTables/Datas/Character/#CardInfo.xlsx
@@ -1243,7 +1243,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>获得 {D} 点护甲，并施加 [寒冷] (受击时 [推迟] 来源)。</t>
+          <t>获得 {D} 点护甲，并施加 [寒冷] 。</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>造成 {A} 点伤害并施加 [定身] (无法移动)。</t>
+          <t>造成 {A} 点伤害并施加 [定身] 。</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>造成 {A} 点伤害，并对目标施加 [破韧] {V}（累计承受 {V} 点伤害后行动被打断）。</t>
+          <t>造成 {A} 点伤害，并对目标施加 [破韧] {V}。</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>获得 [力量] {V}（攻击伤害 +{V}，持续 2 回合）。</t>
+          <t>获得 [力量] {V}。</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2513,7 +2513,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>获得 {D} 点护甲，并获得 [敏捷] {V}（防御牌额外 +{V} 护甲）。</t>
+          <t>获得 {D} 点护甲，并获得 [敏捷] {V}。</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>造成 {A} 点伤害，并使目标 [晕眩] {V} 回合（打断其正在执行的行动）。</t>
+          <t>造成 {A} 点伤害，并使目标 [晕眩] {V} 回合。</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>造成 {A} 点伤害，并施加 [燃烧] {V}（每回合开始受到 {V} 点伤害，持续 3 回合）。</t>
+          <t>造成 {A} 点伤害，并施加 [燃烧] {V}。</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2678,7 +2678,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>获得 [圣物] {V}（接下来 {V} 次 debuff 被自动抵消）。</t>
+          <t>获得 [圣物] {V}。</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>获得 [充能] {V}（下回合开始 +{V} 能量）。</t>
+          <t>获得 [充能] {V}。</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>对目标施加 [虚弱] {V}%（造成伤害降低）和 [脆弱] {V:1}%（受到的伤害提高）。</t>
+          <t>对目标施加 [虚弱] {V}%和 [脆弱] {V:1}%。</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>造成 {A} 点伤害，并施加 [中毒] {V}（每回合开始受到 {V} 点伤害并衰减 1）。</t>
+          <t>造成 {A} 点伤害，并施加 [中毒] {V}。</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>获得 [敏捷] {V}（防御牌额外 +{V} 护甲，持续 2 回合）。</t>
+          <t>获得 [敏捷] {V}。</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>造成 {A} 点伤害，施加 [脆弱] {V}%（获得护甲降低）和 [禁锢] {V:1}（无法移动）。</t>
+          <t>造成 {A} 点伤害，施加 [脆弱] {V}%和 [禁锢] {V:1}。</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>获得 [灵感] {V}（下回合多抽 {V} 张牌）和 [减费] {V:1}（下一张牌费用 -{V:1}）。</t>
+          <t>获得 [灵感] {V}和 [减费] {V:1}。</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">

--- a/DataTables/Datas/Character/#CardInfo.xlsx
+++ b/DataTables/Datas/Character/#CardInfo.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AttackEffect,A,10,false</t>
+          <t>AttackEffect,A,12,false</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AttackExtraEffect,A,8,Channeling|Recoil,2.0</t>
+          <t>AttackExtraEffect,A,9,Channeling|Recoil,2.0</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AttackEffect,A,11,true;DefenseEffect,D,3,true</t>
+          <t>AttackEffect,A,13,true;DefenseEffect,D,3,true</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AttackEffect,A,14,false;PushCollisionEffect,T,1,Stun</t>
+          <t>AttackEffect,A,16,false;PushCollisionEffect,T,1,Stun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>InterceptEffect,D,14</t>
+          <t>InterceptEffect,D,16</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ClearRecoilEffect,N;HealEffect,H,8</t>
+          <t>ClearRecoilEffect,N;HealEffect,H,9</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AttackEffect,A,8,false;AttackConditionalEffect,A,8,IsAttacking</t>
+          <t>AttackEffect,A,9,false;AttackConditionalEffect,A,9,IsAttacking</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AttackEffect,A,14,false</t>
+          <t>AttackEffect,A,16,false</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AttackEffect,A,11,false;PushCollisionEffect,T,1,None</t>
+          <t>AttackEffect,A,13,false;PushCollisionEffect,T,1,None</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AttackEffect,A,4,false;AttackEffect,A,4,false;AttackEffect,A,4,false</t>
+          <t>AttackEffect,A,5,false;AttackEffect,A,5,false;AttackEffect,A,5,false</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AttackExtraEffect,A,25,Burn,2.0</t>
+          <t>AttackExtraEffect,A,29,Burn,2.0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AttackEffect,A,18,true;TimeShiftAllEffect,T,1</t>
+          <t>AttackEffect,A,21,true;TimeShiftAllEffect,T,1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AttackExtraEffect,A,16,Channeling|Recoil,2.0</t>
+          <t>AttackExtraEffect,A,18,Channeling|Recoil,2.0</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AttackEffect,A,4,false;AttackConditionalEffect,A,6,InExecution</t>
+          <t>AttackEffect,A,5,false;AttackConditionalEffect,A,7,InExecution</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AttackExtraEffect,A,14,SkippedLastExecution,2.0</t>
+          <t>AttackExtraEffect,A,16,SkippedLastExecution,2.0</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AttackEffect,A,12,false</t>
+          <t>AttackEffect,A,14,false</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AttackEffect,A,15,false;PushCollisionEffect,T,2,Stun</t>
+          <t>AttackEffect,A,17,false;PushCollisionEffect,T,2,Stun</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AttackEffect,A,8,false;AttackEffect,A,8,false</t>
+          <t>AttackEffect,A,9,false;AttackEffect,A,9,false</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AttackEffect,A,14,true</t>
+          <t>AttackEffect,A,16,true</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AttackExtraEffect,A,25,FullHP,2.0</t>
+          <t>AttackExtraEffect,A,29,FullHP,2.0</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AttackEffect,A,8,false;PushCollisionEffect,T,1,None</t>
+          <t>AttackEffect,A,9,false;PushCollisionEffect,T,1,None</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AttackEffect,A,12,false;AttackConditionalEffect,A,12,IsAttacking</t>
+          <t>AttackEffect,A,14,false;AttackConditionalEffect,A,14,IsAttacking</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AttackEffect,A,10,true;AttackEffect,A,10,true;AttackEffect,A,10,true</t>
+          <t>AttackEffect,A,12,true;AttackEffect,A,12,true;AttackEffect,A,12,true</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AttackExtraEffect,A,18,Pierce,1.0</t>
+          <t>AttackExtraEffect,A,21,Pierce,1.0</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">

--- a/DataTables/Datas/Character/#CardInfo.xlsx
+++ b/DataTables/Datas/Character/#CardInfo.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O105"/>
+  <dimension ref="A1:O108"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>BuffEffect,F,DrawCard,1</t>
+          <t>DrawEffect,F,1</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>SingleAlly</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>SingleAlly</t>
+          <t>Self</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4276,6 +4276,183 @@
         <is>
           <t>FALSE</t>
         </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Irene000</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>[移动]</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>MovePositionEffect,N,Toggle</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Irene</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="b">
+        <v>1</v>
+      </c>
+      <c r="O106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Rocket000</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>[移动]</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>MovePositionEffect,N,Toggle</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Rocket</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="b">
+        <v>1</v>
+      </c>
+      <c r="O107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Zhouzhou000</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>移动</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>[移动]</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>MovePositionEffect,N,Toggle</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Zhouzhou</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="b">
+        <v>1</v>
+      </c>
+      <c r="O108" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/Character/#CardInfo.xlsx
+++ b/DataTables/Datas/Character/#CardInfo.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q138"/>
+  <dimension ref="A1:R138"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1122,6 +1122,11 @@
           <t>CastZone</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>IsInUpgrade</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1209,6 +1214,11 @@
           <t>TargetZoneEnum</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1296,6 +1306,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -1371,6 +1384,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -1446,6 +1462,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -1521,6 +1540,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -1594,6 +1616,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -1669,6 +1694,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -1744,6 +1772,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -1819,6 +1850,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1898,6 +1932,9 @@
         <is>
           <t>Any</t>
         </is>
+      </c>
+      <c r="R13" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14"/>
@@ -1998,6 +2035,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R40" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
@@ -2071,6 +2111,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R41" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
@@ -2144,6 +2187,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R42" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -2217,6 +2263,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R43" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
@@ -2292,6 +2341,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R44" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -2365,6 +2417,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R45" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
@@ -2438,6 +2493,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R46" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
@@ -2511,6 +2569,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R47" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
@@ -2586,6 +2647,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R48" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
@@ -2659,6 +2723,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
@@ -2732,6 +2799,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R50" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
@@ -2805,6 +2875,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R51" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -2878,6 +2951,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R52" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
@@ -2951,6 +3027,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R53" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
@@ -3024,6 +3103,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R54" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
@@ -3097,6 +3179,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R55" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
@@ -3170,6 +3255,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R56" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
@@ -3243,6 +3331,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R57" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
@@ -3316,6 +3407,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R58" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="B59" t="inlineStr">
@@ -3389,6 +3483,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R59" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
@@ -3462,6 +3559,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R60" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -3535,6 +3635,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R61" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="B62" t="inlineStr">
@@ -3607,6 +3710,9 @@
         <is>
           <t>Any</t>
         </is>
+      </c>
+      <c r="R62" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="63"/>
@@ -3729,6 +3835,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R85" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="B86" t="inlineStr">
@@ -3804,6 +3913,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R86" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="87">
       <c r="B87" t="inlineStr">
@@ -3877,6 +3989,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R87" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="B88" t="inlineStr">
@@ -3950,6 +4065,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R88" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="B89" t="inlineStr">
@@ -4025,6 +4143,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R89" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="B90" t="inlineStr">
@@ -4098,6 +4219,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R90" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="B91" t="inlineStr">
@@ -4171,6 +4295,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R91" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="B92" t="inlineStr">
@@ -4246,6 +4373,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R92" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="93">
       <c r="B93" t="inlineStr">
@@ -4321,6 +4451,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R93" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="94">
       <c r="B94" t="inlineStr">
@@ -4394,6 +4527,9 @@
           <t>Back</t>
         </is>
       </c>
+      <c r="R94" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
@@ -4469,6 +4605,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R95" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="B96" t="inlineStr">
@@ -4544,6 +4683,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R96" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="B97" t="inlineStr">
@@ -4617,6 +4759,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R97" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="B98" t="inlineStr">
@@ -4690,6 +4835,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R98" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="B99" t="inlineStr">
@@ -4763,6 +4911,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R99" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="B100" t="inlineStr">
@@ -4836,6 +4987,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R100" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="B101" t="inlineStr">
@@ -4909,6 +5063,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R101" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="102">
       <c r="B102" t="inlineStr">
@@ -4982,6 +5139,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R102" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="103">
       <c r="B103" t="inlineStr">
@@ -5055,6 +5215,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R103" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="B104" t="inlineStr">
@@ -5127,6 +5290,9 @@
         <is>
           <t>Any</t>
         </is>
+      </c>
+      <c r="R104" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="105"/>
@@ -5215,6 +5381,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R119" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="120">
       <c r="B120" t="inlineStr">
@@ -5288,6 +5457,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R120" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="121">
       <c r="B121" t="inlineStr">
@@ -5361,6 +5533,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R121" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="122">
       <c r="B122" t="inlineStr">
@@ -5434,6 +5609,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R122" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="123">
       <c r="B123" t="inlineStr">
@@ -5507,6 +5685,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R123" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="124">
       <c r="B124" t="inlineStr">
@@ -5580,6 +5761,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R124" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="125">
       <c r="B125" t="inlineStr">
@@ -5653,6 +5837,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R125" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="126">
       <c r="B126" t="inlineStr">
@@ -5726,6 +5913,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R126" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="127">
       <c r="B127" t="inlineStr">
@@ -5799,6 +5989,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R127" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5879,6 +6072,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R128" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5959,6 +6155,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R129" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6039,6 +6238,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R130" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6118,6 +6320,9 @@
         <is>
           <t>Any</t>
         </is>
+      </c>
+      <c r="R131" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="132"/>
@@ -6192,6 +6397,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R136" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="B137" t="inlineStr">
@@ -6261,6 +6469,9 @@
           <t>Any</t>
         </is>
       </c>
+      <c r="R137" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="138">
       <c r="B138" t="inlineStr">
@@ -6329,6 +6540,9 @@
         <is>
           <t>Any</t>
         </is>
+      </c>
+      <c r="R138" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6358,7 +6572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.026548672566371" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <sheetData>
     <row r="1">
@@ -6447,6 +6661,11 @@
           <t>CastZone</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>IsInUpgrade</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -6534,6 +6753,11 @@
           <t>TargetZoneEnum</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6615,6 +6839,9 @@
         <is>
           <t>Any</t>
         </is>
+      </c>
+      <c r="R5" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
